--- a/import_siswa_sikapdik/Template_Import_Siswa_SIKAPDIK_Kelas2.xlsx
+++ b/import_siswa_sikapdik/Template_Import_Siswa_SIKAPDIK_Kelas2.xlsx
@@ -642,9 +642,21 @@
           <t>Meyssa Clara Natania</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2017</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 02/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -670,9 +682,21 @@
           <t>Queensha Trias Anindhita</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Tangerang Selatan</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>09/07/2018</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar I, RT 01/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -698,9 +722,21 @@
           <t>Rafadan Al Gafin</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>11/04/2018</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 02/RW 03, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -726,9 +762,21 @@
           <t>Ridho Ramdan Alhafis</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2018</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar I, RT 01/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -754,9 +802,21 @@
           <t>Rifqi Fathan</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>04/02/2018</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 02/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -782,9 +842,21 @@
           <t>Syakilla Zulfa Naufalin</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>20/01/2018</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar I, RT 02/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -810,9 +882,21 @@
           <t>Villa Akbar Vaudria Mahmuda</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>17/05/2018</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar I, RT 02/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
